--- a/DangNhapVaDuAn.xlsx
+++ b/DangNhapVaDuAn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BDF681-8F20-4E0F-83AC-BFD842B0E2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C4617B-D5EE-49D8-83B2-57AFAAF60885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D15556D2-2B15-4E64-94D9-3621949CCF05}"/>
   </bookViews>
@@ -251,9 +251,6 @@
     <t>Giúp người dùng sử dụng các chức năng quản lý dự án</t>
   </si>
   <si>
-    <t>Xem danh sách công việc</t>
-  </si>
-  <si>
     <t>Quản lý các công việc của 1 dự án cụ thể</t>
   </si>
   <si>
@@ -294,9 +291,6 @@
     <t>Có thể thêm filter nâng cao</t>
   </si>
   <si>
-    <t>Xem danh sách dự án</t>
-  </si>
-  <si>
     <t>Hiện ra danh sách dự án mà nhân viên đó đang tham gia</t>
   </si>
   <si>
@@ -332,6 +326,12 @@
   </si>
   <si>
     <t>Nhân viên chỉ xem được các dự án mà họ có quyền truy cập</t>
+  </si>
+  <si>
+    <t>UC 08_01 Xem danh sách công việc</t>
+  </si>
+  <si>
+    <t>UC 08_02 Xem danh sách dự án</t>
   </si>
 </sst>
 </file>
@@ -701,29 +701,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1314,11 +1314,11 @@
       <c r="A20" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="24"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="27"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -1327,10 +1327,10 @@
       <c r="B21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="28">
         <v>46112</v>
       </c>
-      <c r="D21" s="24"/>
+      <c r="D21" s="27"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -1339,8 +1339,8 @@
       <c r="B22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="27"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
@@ -1368,7 +1368,7 @@
       <c r="A25" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="29" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="20"/>
@@ -1379,7 +1379,7 @@
       <c r="A26" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="29" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="20"/>
@@ -1390,7 +1390,7 @@
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="29" t="s">
         <v>39</v>
       </c>
       <c r="C27" s="20"/>
@@ -1401,7 +1401,7 @@
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="20"/>
@@ -1446,7 +1446,7 @@
         <v>13</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21"/>
@@ -1457,7 +1457,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21"/>
@@ -1468,7 +1468,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21"/>
@@ -1489,23 +1489,23 @@
       <c r="F36" s="10"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="24"/>
       <c r="F37" s="9"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="24"/>
+      <c r="B38" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27"/>
       <c r="F38" s="10"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1515,10 +1515,10 @@
       <c r="B39" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="28">
         <v>46112</v>
       </c>
-      <c r="D39" s="24"/>
+      <c r="D39" s="27"/>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1528,8 +1528,8 @@
       <c r="B40" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="23"/>
-      <c r="D40" s="24"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="27"/>
       <c r="F40" s="10"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1537,7 +1537,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="21"/>
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21"/>
@@ -1557,8 +1557,8 @@
       <c r="A43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="22" t="s">
-        <v>45</v>
+      <c r="B43" s="29" t="s">
+        <v>44</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="21"/>
@@ -1568,7 +1568,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="21"/>
@@ -1577,8 +1577,8 @@
       <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="22" t="s">
-        <v>47</v>
+      <c r="B45" s="29" t="s">
+        <v>46</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21"/>
@@ -1588,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="21"/>
@@ -1628,7 +1628,7 @@
         <v>13</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21"/>
@@ -1638,7 +1638,7 @@
         <v>14</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="21"/>
@@ -1648,7 +1648,7 @@
         <v>15</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C52" s="20"/>
       <c r="D52" s="21"/>
@@ -1666,22 +1666,22 @@
       <c r="D54" s="18"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="27"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="24"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B56" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="24"/>
+      <c r="B56" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="27"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -1690,10 +1690,10 @@
       <c r="B57" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="28">
         <v>46112</v>
       </c>
-      <c r="D57" s="24"/>
+      <c r="D57" s="27"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -1702,15 +1702,15 @@
       <c r="B58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="23"/>
-      <c r="D58" s="24"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="27"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C59" s="20"/>
       <c r="D59" s="21"/>
@@ -1720,7 +1720,7 @@
         <v>5</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21"/>
@@ -1729,8 +1729,8 @@
       <c r="A61" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="22" t="s">
-        <v>56</v>
+      <c r="B61" s="29" t="s">
+        <v>54</v>
       </c>
       <c r="C61" s="20"/>
       <c r="D61" s="21"/>
@@ -1740,7 +1740,7 @@
         <v>7</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C62" s="20"/>
       <c r="D62" s="21"/>
@@ -1749,8 +1749,8 @@
       <c r="A63" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B63" s="22" t="s">
-        <v>59</v>
+      <c r="B63" s="29" t="s">
+        <v>57</v>
       </c>
       <c r="C63" s="20"/>
       <c r="D63" s="21"/>
@@ -1759,8 +1759,8 @@
       <c r="A64" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B64" s="22" t="s">
-        <v>60</v>
+      <c r="B64" s="29" t="s">
+        <v>58</v>
       </c>
       <c r="C64" s="20"/>
       <c r="D64" s="21"/>
@@ -1770,7 +1770,7 @@
         <v>10</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C65" s="20"/>
       <c r="D65" s="21"/>
@@ -1800,7 +1800,7 @@
         <v>13</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="21"/>
@@ -1810,7 +1810,7 @@
         <v>14</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="21"/>
@@ -1820,7 +1820,7 @@
         <v>15</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C70" s="30"/>
       <c r="D70" s="30"/>
@@ -1836,33 +1836,27 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C22:D22"/>
@@ -1879,27 +1873,33 @@
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="A37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
